--- a/artfynd/A 30035-2024 artfynd.xlsx
+++ b/artfynd/A 30035-2024 artfynd.xlsx
@@ -1683,12 +1683,7 @@
         <v>94391986</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,10 +1723,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404720.0846839676</v>
+        <v>404720</v>
       </c>
       <c r="R10" t="n">
-        <v>7014286.091512644</v>
+        <v>7014286</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1761,19 +1756,9 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 30035-2024 artfynd.xlsx
+++ b/artfynd/A 30035-2024 artfynd.xlsx
@@ -1683,7 +1683,7 @@
         <v>94391986</v>
       </c>
       <c r="B10" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30035-2024 artfynd.xlsx
+++ b/artfynd/A 30035-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94391976</v>
+        <v>94391974</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404759.62109741</v>
+        <v>404739</v>
       </c>
       <c r="R2" t="n">
-        <v>7014539.183312771</v>
+        <v>7014468</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,17 +759,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,12 +790,7 @@
         <v>94391980</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404759.6876859402</v>
+        <v>404760</v>
       </c>
       <c r="R3" t="n">
-        <v>7014541.435340984</v>
+        <v>7014542</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +855,9 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94391972</v>
+        <v>94391988</v>
       </c>
       <c r="B4" t="n">
-        <v>89777</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,32 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>2081</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Betespräglad skog vid Ytterstvallen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404734.9900989033</v>
+        <v>404744</v>
       </c>
       <c r="R4" t="n">
-        <v>7014454.258624552</v>
+        <v>7014219</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,44 +967,33 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1055,37 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94391992</v>
+        <v>94391994</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1095,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404737.6582054375</v>
+        <v>404807</v>
       </c>
       <c r="R5" t="n">
-        <v>7014468.154846816</v>
+        <v>7014498</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,26 +1079,16 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1182,50 +1123,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94391994</v>
+        <v>94391983</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Betespräglad skog vid Ytterstvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>404807.1599961995</v>
+        <v>404892</v>
       </c>
       <c r="R6" t="n">
-        <v>7014498.107437558</v>
+        <v>7014119</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,44 +1195,20 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1309,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94391988</v>
+        <v>94391993</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1349,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404743.8369360006</v>
+        <v>404827</v>
       </c>
       <c r="R7" t="n">
-        <v>7014219.115631181</v>
+        <v>7014625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,43 +1293,33 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1436,15 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94391983</v>
+        <v>94391992</v>
       </c>
       <c r="B8" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,38 +1348,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Betespräglad skog vid Ytterstvallen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404892.1247280383</v>
+        <v>404738</v>
       </c>
       <c r="R8" t="n">
-        <v>7014119.154016766</v>
+        <v>7014468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1513,30 +1405,34 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1553,15 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94391974</v>
+        <v>94391986</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,34 +1460,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Betespräglad skog vid Ytterstvallen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404738.5602671365</v>
+        <v>404720</v>
       </c>
       <c r="R9" t="n">
-        <v>7014468.128169148</v>
+        <v>7014286</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1626,19 +1525,14 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,21 +1543,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1680,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94391986</v>
+        <v>94391972</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>92329</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,31 +1570,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1723,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404720</v>
+        <v>404735</v>
       </c>
       <c r="R10" t="n">
-        <v>7014286</v>
+        <v>7014454</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1761,19 +1635,30 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 30035-2024 artfynd.xlsx
+++ b/artfynd/A 30035-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391974</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391980</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391988</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391994</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391983</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391993</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391992</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391986</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1672,8 +1717,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391972</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>